--- a/artfynd/A 19019-2024 artfynd.xlsx
+++ b/artfynd/A 19019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121471890</v>
+        <v>121471892</v>
       </c>
       <c r="B2" t="n">
-        <v>94584</v>
+        <v>80252</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428698</v>
+        <v>428712</v>
       </c>
       <c r="R2" t="n">
-        <v>6232878</v>
+        <v>6232901</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471884</v>
+        <v>121471888</v>
       </c>
       <c r="B3" t="n">
-        <v>80239</v>
+        <v>74522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230185</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428533</v>
+        <v>428627</v>
       </c>
       <c r="R3" t="n">
-        <v>6232951</v>
+        <v>6232838</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471892</v>
+        <v>121471890</v>
       </c>
       <c r="B4" t="n">
-        <v>80252</v>
+        <v>94584</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428712</v>
+        <v>428698</v>
       </c>
       <c r="R4" t="n">
-        <v>6232901</v>
+        <v>6232878</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471891</v>
+        <v>121471884</v>
       </c>
       <c r="B6" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428714</v>
+        <v>428533</v>
       </c>
       <c r="R6" t="n">
-        <v>6232900</v>
+        <v>6232951</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471888</v>
+        <v>121471889</v>
       </c>
       <c r="B7" t="n">
-        <v>74522</v>
+        <v>96721</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6428</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428627</v>
+        <v>428662</v>
       </c>
       <c r="R7" t="n">
-        <v>6232838</v>
+        <v>6232900</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471883</v>
+        <v>121471891</v>
       </c>
       <c r="B8" t="n">
         <v>96721</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428493</v>
+        <v>428714</v>
       </c>
       <c r="R8" t="n">
-        <v>6232948</v>
+        <v>6232900</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471889</v>
+        <v>121471893</v>
       </c>
       <c r="B9" t="n">
         <v>96721</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428662</v>
+        <v>428735</v>
       </c>
       <c r="R9" t="n">
-        <v>6232900</v>
+        <v>6232886</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471893</v>
+        <v>121471883</v>
       </c>
       <c r="B10" t="n">
         <v>96721</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428735</v>
+        <v>428493</v>
       </c>
       <c r="R10" t="n">
-        <v>6232886</v>
+        <v>6232948</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 19019-2024 artfynd.xlsx
+++ b/artfynd/A 19019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121471892</v>
+        <v>121471888</v>
       </c>
       <c r="B2" t="n">
-        <v>80252</v>
+        <v>74522</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1144</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428712</v>
+        <v>428627</v>
       </c>
       <c r="R2" t="n">
-        <v>6232901</v>
+        <v>6232838</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471888</v>
+        <v>121471890</v>
       </c>
       <c r="B3" t="n">
-        <v>74522</v>
+        <v>94585</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428627</v>
+        <v>428698</v>
       </c>
       <c r="R3" t="n">
-        <v>6232838</v>
+        <v>6232878</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471890</v>
+        <v>121471883</v>
       </c>
       <c r="B4" t="n">
-        <v>94584</v>
+        <v>96722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428698</v>
+        <v>428493</v>
       </c>
       <c r="R4" t="n">
-        <v>6232878</v>
+        <v>6232948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471894</v>
+        <v>121471889</v>
       </c>
       <c r="B5" t="n">
-        <v>94584</v>
+        <v>96722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428734</v>
+        <v>428662</v>
       </c>
       <c r="R5" t="n">
-        <v>6232888</v>
+        <v>6232900</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471884</v>
+        <v>121471893</v>
       </c>
       <c r="B6" t="n">
-        <v>80239</v>
+        <v>96722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428533</v>
+        <v>428735</v>
       </c>
       <c r="R6" t="n">
-        <v>6232951</v>
+        <v>6232886</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471889</v>
+        <v>121471892</v>
       </c>
       <c r="B7" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428662</v>
+        <v>428712</v>
       </c>
       <c r="R7" t="n">
-        <v>6232900</v>
+        <v>6232901</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471891</v>
+        <v>121471894</v>
       </c>
       <c r="B8" t="n">
-        <v>96721</v>
+        <v>94585</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428714</v>
+        <v>428734</v>
       </c>
       <c r="R8" t="n">
-        <v>6232900</v>
+        <v>6232888</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471893</v>
+        <v>121471884</v>
       </c>
       <c r="B9" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428735</v>
+        <v>428533</v>
       </c>
       <c r="R9" t="n">
-        <v>6232886</v>
+        <v>6232951</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471883</v>
+        <v>121471891</v>
       </c>
       <c r="B10" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428493</v>
+        <v>428714</v>
       </c>
       <c r="R10" t="n">
-        <v>6232948</v>
+        <v>6232900</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 19019-2024 artfynd.xlsx
+++ b/artfynd/A 19019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121471888</v>
+        <v>121471892</v>
       </c>
       <c r="B2" t="n">
-        <v>74522</v>
+        <v>80255</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>1144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428627</v>
+        <v>428712</v>
       </c>
       <c r="R2" t="n">
-        <v>6232838</v>
+        <v>6232901</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471890</v>
+        <v>121471894</v>
       </c>
       <c r="B3" t="n">
-        <v>94585</v>
+        <v>94588</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428698</v>
+        <v>428734</v>
       </c>
       <c r="R3" t="n">
-        <v>6232878</v>
+        <v>6232888</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>121471883</v>
       </c>
       <c r="B4" t="n">
-        <v>96722</v>
+        <v>96725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471889</v>
+        <v>121471890</v>
       </c>
       <c r="B5" t="n">
-        <v>96722</v>
+        <v>94588</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428662</v>
+        <v>428698</v>
       </c>
       <c r="R5" t="n">
-        <v>6232900</v>
+        <v>6232878</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471893</v>
+        <v>121471891</v>
       </c>
       <c r="B6" t="n">
-        <v>96722</v>
+        <v>96725</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428735</v>
+        <v>428714</v>
       </c>
       <c r="R6" t="n">
-        <v>6232886</v>
+        <v>6232900</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471892</v>
+        <v>121471889</v>
       </c>
       <c r="B7" t="n">
-        <v>80252</v>
+        <v>96725</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428712</v>
+        <v>428662</v>
       </c>
       <c r="R7" t="n">
-        <v>6232901</v>
+        <v>6232900</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471894</v>
+        <v>121471893</v>
       </c>
       <c r="B8" t="n">
-        <v>94585</v>
+        <v>96725</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428734</v>
+        <v>428735</v>
       </c>
       <c r="R8" t="n">
-        <v>6232888</v>
+        <v>6232886</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471884</v>
+        <v>121471888</v>
       </c>
       <c r="B9" t="n">
-        <v>80239</v>
+        <v>74525</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230185</v>
+        <v>6428</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428533</v>
+        <v>428627</v>
       </c>
       <c r="R9" t="n">
-        <v>6232951</v>
+        <v>6232838</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471891</v>
+        <v>121471884</v>
       </c>
       <c r="B10" t="n">
-        <v>96722</v>
+        <v>80242</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428714</v>
+        <v>428533</v>
       </c>
       <c r="R10" t="n">
-        <v>6232900</v>
+        <v>6232951</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 19019-2024 artfynd.xlsx
+++ b/artfynd/A 19019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121471892</v>
+        <v>121471894</v>
       </c>
       <c r="B2" t="n">
-        <v>80255</v>
+        <v>94588</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428712</v>
+        <v>428734</v>
       </c>
       <c r="R2" t="n">
-        <v>6232901</v>
+        <v>6232888</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471894</v>
+        <v>121471889</v>
       </c>
       <c r="B3" t="n">
-        <v>94588</v>
+        <v>96725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428734</v>
+        <v>428662</v>
       </c>
       <c r="R3" t="n">
-        <v>6232888</v>
+        <v>6232900</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471883</v>
+        <v>121471891</v>
       </c>
       <c r="B4" t="n">
         <v>96725</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428493</v>
+        <v>428714</v>
       </c>
       <c r="R4" t="n">
-        <v>6232948</v>
+        <v>6232900</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471890</v>
+        <v>121471884</v>
       </c>
       <c r="B5" t="n">
-        <v>94588</v>
+        <v>80242</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428698</v>
+        <v>428533</v>
       </c>
       <c r="R5" t="n">
-        <v>6232878</v>
+        <v>6232951</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471891</v>
+        <v>121471893</v>
       </c>
       <c r="B6" t="n">
         <v>96725</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428714</v>
+        <v>428735</v>
       </c>
       <c r="R6" t="n">
-        <v>6232900</v>
+        <v>6232886</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471889</v>
+        <v>121471888</v>
       </c>
       <c r="B7" t="n">
-        <v>96725</v>
+        <v>74525</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>6428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428662</v>
+        <v>428627</v>
       </c>
       <c r="R7" t="n">
-        <v>6232900</v>
+        <v>6232838</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471893</v>
+        <v>121471890</v>
       </c>
       <c r="B8" t="n">
-        <v>96725</v>
+        <v>94588</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428735</v>
+        <v>428698</v>
       </c>
       <c r="R8" t="n">
-        <v>6232886</v>
+        <v>6232878</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471888</v>
+        <v>121471892</v>
       </c>
       <c r="B9" t="n">
-        <v>74525</v>
+        <v>80255</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6428</v>
+        <v>1144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428627</v>
+        <v>428712</v>
       </c>
       <c r="R9" t="n">
-        <v>6232838</v>
+        <v>6232901</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471884</v>
+        <v>121471883</v>
       </c>
       <c r="B10" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428533</v>
+        <v>428493</v>
       </c>
       <c r="R10" t="n">
-        <v>6232951</v>
+        <v>6232948</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 19019-2024 artfynd.xlsx
+++ b/artfynd/A 19019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121471894</v>
+        <v>121471889</v>
       </c>
       <c r="B2" t="n">
-        <v>94588</v>
+        <v>96731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428734</v>
+        <v>428662</v>
       </c>
       <c r="R2" t="n">
-        <v>6232888</v>
+        <v>6232900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471889</v>
+        <v>121471884</v>
       </c>
       <c r="B3" t="n">
-        <v>96725</v>
+        <v>80243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428662</v>
+        <v>428533</v>
       </c>
       <c r="R3" t="n">
-        <v>6232900</v>
+        <v>6232951</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471891</v>
+        <v>121471892</v>
       </c>
       <c r="B4" t="n">
-        <v>96725</v>
+        <v>80256</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428714</v>
+        <v>428712</v>
       </c>
       <c r="R4" t="n">
-        <v>6232900</v>
+        <v>6232901</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471884</v>
+        <v>121471891</v>
       </c>
       <c r="B5" t="n">
-        <v>80242</v>
+        <v>96731</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428533</v>
+        <v>428714</v>
       </c>
       <c r="R5" t="n">
-        <v>6232951</v>
+        <v>6232900</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471893</v>
+        <v>121471888</v>
       </c>
       <c r="B6" t="n">
-        <v>96725</v>
+        <v>74526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2606</v>
+        <v>6428</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428735</v>
+        <v>428627</v>
       </c>
       <c r="R6" t="n">
-        <v>6232886</v>
+        <v>6232838</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471888</v>
+        <v>121471890</v>
       </c>
       <c r="B7" t="n">
-        <v>74525</v>
+        <v>94594</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6428</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428627</v>
+        <v>428698</v>
       </c>
       <c r="R7" t="n">
-        <v>6232838</v>
+        <v>6232878</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471890</v>
+        <v>121471883</v>
       </c>
       <c r="B8" t="n">
-        <v>94588</v>
+        <v>96731</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428698</v>
+        <v>428493</v>
       </c>
       <c r="R8" t="n">
-        <v>6232878</v>
+        <v>6232948</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471892</v>
+        <v>121471894</v>
       </c>
       <c r="B9" t="n">
-        <v>80255</v>
+        <v>94594</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428712</v>
+        <v>428734</v>
       </c>
       <c r="R9" t="n">
-        <v>6232901</v>
+        <v>6232888</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471883</v>
+        <v>121471893</v>
       </c>
       <c r="B10" t="n">
-        <v>96725</v>
+        <v>96731</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428493</v>
+        <v>428735</v>
       </c>
       <c r="R10" t="n">
-        <v>6232948</v>
+        <v>6232886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 19019-2024 artfynd.xlsx
+++ b/artfynd/A 19019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121471889</v>
+        <v>121471890</v>
       </c>
       <c r="B2" t="n">
-        <v>96731</v>
+        <v>94595</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428662</v>
+        <v>428698</v>
       </c>
       <c r="R2" t="n">
-        <v>6232900</v>
+        <v>6232878</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471884</v>
+        <v>121471893</v>
       </c>
       <c r="B3" t="n">
-        <v>80243</v>
+        <v>96732</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428533</v>
+        <v>428735</v>
       </c>
       <c r="R3" t="n">
-        <v>6232951</v>
+        <v>6232886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471892</v>
+        <v>121471883</v>
       </c>
       <c r="B4" t="n">
-        <v>80256</v>
+        <v>96732</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428712</v>
+        <v>428493</v>
       </c>
       <c r="R4" t="n">
-        <v>6232901</v>
+        <v>6232948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>121471891</v>
       </c>
       <c r="B5" t="n">
-        <v>96731</v>
+        <v>96732</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471888</v>
+        <v>121471884</v>
       </c>
       <c r="B6" t="n">
-        <v>74526</v>
+        <v>80244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>230185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428627</v>
+        <v>428533</v>
       </c>
       <c r="R6" t="n">
-        <v>6232838</v>
+        <v>6232951</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471890</v>
+        <v>121471894</v>
       </c>
       <c r="B7" t="n">
-        <v>94594</v>
+        <v>94595</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428698</v>
+        <v>428734</v>
       </c>
       <c r="R7" t="n">
-        <v>6232878</v>
+        <v>6232888</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471883</v>
+        <v>121471889</v>
       </c>
       <c r="B8" t="n">
-        <v>96731</v>
+        <v>96732</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428493</v>
+        <v>428662</v>
       </c>
       <c r="R8" t="n">
-        <v>6232948</v>
+        <v>6232900</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471894</v>
+        <v>121471892</v>
       </c>
       <c r="B9" t="n">
-        <v>94594</v>
+        <v>80257</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428734</v>
+        <v>428712</v>
       </c>
       <c r="R9" t="n">
-        <v>6232888</v>
+        <v>6232901</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471893</v>
+        <v>121471888</v>
       </c>
       <c r="B10" t="n">
-        <v>96731</v>
+        <v>74527</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2606</v>
+        <v>6428</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428735</v>
+        <v>428627</v>
       </c>
       <c r="R10" t="n">
-        <v>6232886</v>
+        <v>6232838</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 19019-2024 artfynd.xlsx
+++ b/artfynd/A 19019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121471890</v>
+        <v>121471891</v>
       </c>
       <c r="B2" t="n">
-        <v>94595</v>
+        <v>96732</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428698</v>
+        <v>428714</v>
       </c>
       <c r="R2" t="n">
-        <v>6232878</v>
+        <v>6232900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471893</v>
+        <v>121471892</v>
       </c>
       <c r="B3" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428735</v>
+        <v>428712</v>
       </c>
       <c r="R3" t="n">
-        <v>6232886</v>
+        <v>6232901</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471883</v>
+        <v>121471888</v>
       </c>
       <c r="B4" t="n">
-        <v>96732</v>
+        <v>74527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2606</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428493</v>
+        <v>428627</v>
       </c>
       <c r="R4" t="n">
-        <v>6232948</v>
+        <v>6232838</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471891</v>
+        <v>121471884</v>
       </c>
       <c r="B5" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428714</v>
+        <v>428533</v>
       </c>
       <c r="R5" t="n">
-        <v>6232900</v>
+        <v>6232951</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471884</v>
+        <v>121471890</v>
       </c>
       <c r="B6" t="n">
-        <v>80244</v>
+        <v>94595</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428533</v>
+        <v>428698</v>
       </c>
       <c r="R6" t="n">
-        <v>6232951</v>
+        <v>6232878</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471889</v>
+        <v>121471893</v>
       </c>
       <c r="B8" t="n">
         <v>96732</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428662</v>
+        <v>428735</v>
       </c>
       <c r="R8" t="n">
-        <v>6232900</v>
+        <v>6232886</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471892</v>
+        <v>121471889</v>
       </c>
       <c r="B9" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428712</v>
+        <v>428662</v>
       </c>
       <c r="R9" t="n">
-        <v>6232901</v>
+        <v>6232900</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471888</v>
+        <v>121471883</v>
       </c>
       <c r="B10" t="n">
-        <v>74527</v>
+        <v>96732</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6428</v>
+        <v>2606</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428627</v>
+        <v>428493</v>
       </c>
       <c r="R10" t="n">
-        <v>6232838</v>
+        <v>6232948</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 19019-2024 artfynd.xlsx
+++ b/artfynd/A 19019-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121471891</v>
+        <v>121471889</v>
       </c>
       <c r="B2" t="n">
         <v>96732</v>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428714</v>
+        <v>428662</v>
       </c>
       <c r="R2" t="n">
         <v>6232900</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471892</v>
+        <v>121471883</v>
       </c>
       <c r="B3" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428712</v>
+        <v>428493</v>
       </c>
       <c r="R3" t="n">
-        <v>6232901</v>
+        <v>6232948</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471888</v>
+        <v>121471891</v>
       </c>
       <c r="B4" t="n">
-        <v>74527</v>
+        <v>96732</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428627</v>
+        <v>428714</v>
       </c>
       <c r="R4" t="n">
-        <v>6232838</v>
+        <v>6232900</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471884</v>
+        <v>121471888</v>
       </c>
       <c r="B5" t="n">
-        <v>80244</v>
+        <v>74527</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230185</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428533</v>
+        <v>428627</v>
       </c>
       <c r="R5" t="n">
-        <v>6232951</v>
+        <v>6232838</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471894</v>
+        <v>121471884</v>
       </c>
       <c r="B7" t="n">
-        <v>94595</v>
+        <v>80244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428734</v>
+        <v>428533</v>
       </c>
       <c r="R7" t="n">
-        <v>6232888</v>
+        <v>6232951</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471893</v>
+        <v>121471894</v>
       </c>
       <c r="B8" t="n">
-        <v>96732</v>
+        <v>94595</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428735</v>
+        <v>428734</v>
       </c>
       <c r="R8" t="n">
-        <v>6232886</v>
+        <v>6232888</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471889</v>
+        <v>121471893</v>
       </c>
       <c r="B9" t="n">
         <v>96732</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428662</v>
+        <v>428735</v>
       </c>
       <c r="R9" t="n">
-        <v>6232900</v>
+        <v>6232886</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471883</v>
+        <v>121471892</v>
       </c>
       <c r="B10" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428493</v>
+        <v>428712</v>
       </c>
       <c r="R10" t="n">
-        <v>6232948</v>
+        <v>6232901</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 19019-2024 artfynd.xlsx
+++ b/artfynd/A 19019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121471889</v>
+        <v>121471888</v>
       </c>
       <c r="B2" t="n">
-        <v>96732</v>
+        <v>74527</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2606</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428662</v>
+        <v>428627</v>
       </c>
       <c r="R2" t="n">
-        <v>6232900</v>
+        <v>6232838</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471883</v>
+        <v>121471894</v>
       </c>
       <c r="B3" t="n">
-        <v>96732</v>
+        <v>94595</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428493</v>
+        <v>428734</v>
       </c>
       <c r="R3" t="n">
-        <v>6232948</v>
+        <v>6232888</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471891</v>
+        <v>121471884</v>
       </c>
       <c r="B4" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428714</v>
+        <v>428533</v>
       </c>
       <c r="R4" t="n">
-        <v>6232900</v>
+        <v>6232951</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471888</v>
+        <v>121471893</v>
       </c>
       <c r="B5" t="n">
-        <v>74527</v>
+        <v>96732</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428627</v>
+        <v>428735</v>
       </c>
       <c r="R5" t="n">
-        <v>6232838</v>
+        <v>6232886</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471890</v>
+        <v>121471883</v>
       </c>
       <c r="B6" t="n">
-        <v>94595</v>
+        <v>96732</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428698</v>
+        <v>428493</v>
       </c>
       <c r="R6" t="n">
-        <v>6232878</v>
+        <v>6232948</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471884</v>
+        <v>121471889</v>
       </c>
       <c r="B7" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428533</v>
+        <v>428662</v>
       </c>
       <c r="R7" t="n">
-        <v>6232951</v>
+        <v>6232900</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471894</v>
+        <v>121471891</v>
       </c>
       <c r="B8" t="n">
-        <v>94595</v>
+        <v>96732</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428734</v>
+        <v>428714</v>
       </c>
       <c r="R8" t="n">
-        <v>6232888</v>
+        <v>6232900</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471893</v>
+        <v>121471892</v>
       </c>
       <c r="B9" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428735</v>
+        <v>428712</v>
       </c>
       <c r="R9" t="n">
-        <v>6232886</v>
+        <v>6232901</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471892</v>
+        <v>121471890</v>
       </c>
       <c r="B10" t="n">
-        <v>80257</v>
+        <v>94595</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428712</v>
+        <v>428698</v>
       </c>
       <c r="R10" t="n">
-        <v>6232901</v>
+        <v>6232878</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 19019-2024 artfynd.xlsx
+++ b/artfynd/A 19019-2024 artfynd.xlsx
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471889</v>
+        <v>121471891</v>
       </c>
       <c r="B7" t="n">
         <v>96732</v>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428662</v>
+        <v>428714</v>
       </c>
       <c r="R7" t="n">
         <v>6232900</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471891</v>
+        <v>121471889</v>
       </c>
       <c r="B8" t="n">
         <v>96732</v>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428714</v>
+        <v>428662</v>
       </c>
       <c r="R8" t="n">
         <v>6232900</v>

--- a/artfynd/A 19019-2024 artfynd.xlsx
+++ b/artfynd/A 19019-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121471888</v>
       </c>
       <c r="B2" t="n">
-        <v>74527</v>
+        <v>74534</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471894</v>
+        <v>121471893</v>
       </c>
       <c r="B3" t="n">
-        <v>94595</v>
+        <v>96740</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428734</v>
+        <v>428735</v>
       </c>
       <c r="R3" t="n">
-        <v>6232888</v>
+        <v>6232886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471884</v>
+        <v>121471891</v>
       </c>
       <c r="B4" t="n">
-        <v>80244</v>
+        <v>96740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428533</v>
+        <v>428714</v>
       </c>
       <c r="R4" t="n">
-        <v>6232951</v>
+        <v>6232900</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471893</v>
+        <v>121471889</v>
       </c>
       <c r="B5" t="n">
-        <v>96732</v>
+        <v>96740</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428735</v>
+        <v>428662</v>
       </c>
       <c r="R5" t="n">
-        <v>6232886</v>
+        <v>6232900</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471883</v>
+        <v>121471894</v>
       </c>
       <c r="B6" t="n">
-        <v>96732</v>
+        <v>94603</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428493</v>
+        <v>428734</v>
       </c>
       <c r="R6" t="n">
-        <v>6232948</v>
+        <v>6232888</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471891</v>
+        <v>121471890</v>
       </c>
       <c r="B7" t="n">
-        <v>96732</v>
+        <v>94603</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428714</v>
+        <v>428698</v>
       </c>
       <c r="R7" t="n">
-        <v>6232900</v>
+        <v>6232878</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471889</v>
+        <v>121471884</v>
       </c>
       <c r="B8" t="n">
-        <v>96732</v>
+        <v>80251</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428662</v>
+        <v>428533</v>
       </c>
       <c r="R8" t="n">
-        <v>6232900</v>
+        <v>6232951</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
         <v>121471892</v>
       </c>
       <c r="B9" t="n">
-        <v>80257</v>
+        <v>80264</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471890</v>
+        <v>121471883</v>
       </c>
       <c r="B10" t="n">
-        <v>94595</v>
+        <v>96740</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428698</v>
+        <v>428493</v>
       </c>
       <c r="R10" t="n">
-        <v>6232878</v>
+        <v>6232948</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 19019-2024 artfynd.xlsx
+++ b/artfynd/A 19019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121471893</v>
+        <v>121471884</v>
       </c>
       <c r="B2" t="n">
-        <v>96740</v>
+        <v>80251</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428735</v>
+        <v>428533</v>
       </c>
       <c r="R2" t="n">
-        <v>6232886</v>
+        <v>6232951</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471889</v>
+        <v>121471891</v>
       </c>
       <c r="B3" t="n">
         <v>96740</v>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428662</v>
+        <v>428714</v>
       </c>
       <c r="R3" t="n">
         <v>6232900</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471883</v>
+        <v>121471894</v>
       </c>
       <c r="B4" t="n">
-        <v>96740</v>
+        <v>94603</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428493</v>
+        <v>428734</v>
       </c>
       <c r="R4" t="n">
-        <v>6232948</v>
+        <v>6232888</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471891</v>
+        <v>121471893</v>
       </c>
       <c r="B5" t="n">
         <v>96740</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428714</v>
+        <v>428735</v>
       </c>
       <c r="R5" t="n">
-        <v>6232900</v>
+        <v>6232886</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471890</v>
+        <v>121471883</v>
       </c>
       <c r="B6" t="n">
-        <v>94603</v>
+        <v>96740</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428698</v>
+        <v>428493</v>
       </c>
       <c r="R6" t="n">
-        <v>6232878</v>
+        <v>6232948</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471884</v>
+        <v>121471890</v>
       </c>
       <c r="B7" t="n">
-        <v>80251</v>
+        <v>94603</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428533</v>
+        <v>428698</v>
       </c>
       <c r="R7" t="n">
-        <v>6232951</v>
+        <v>6232878</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471894</v>
+        <v>121471889</v>
       </c>
       <c r="B8" t="n">
-        <v>94603</v>
+        <v>96740</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428734</v>
+        <v>428662</v>
       </c>
       <c r="R8" t="n">
-        <v>6232888</v>
+        <v>6232900</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471892</v>
+        <v>121471888</v>
       </c>
       <c r="B9" t="n">
-        <v>80264</v>
+        <v>74534</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1144</v>
+        <v>6428</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428712</v>
+        <v>428627</v>
       </c>
       <c r="R9" t="n">
-        <v>6232901</v>
+        <v>6232838</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471888</v>
+        <v>121471892</v>
       </c>
       <c r="B10" t="n">
-        <v>74534</v>
+        <v>80264</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6428</v>
+        <v>1144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428627</v>
+        <v>428712</v>
       </c>
       <c r="R10" t="n">
-        <v>6232838</v>
+        <v>6232901</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 19019-2024 artfynd.xlsx
+++ b/artfynd/A 19019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121471884</v>
+        <v>121471893</v>
       </c>
       <c r="B2" t="n">
-        <v>80251</v>
+        <v>96740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428533</v>
+        <v>428735</v>
       </c>
       <c r="R2" t="n">
-        <v>6232951</v>
+        <v>6232886</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471894</v>
+        <v>121471889</v>
       </c>
       <c r="B4" t="n">
-        <v>94603</v>
+        <v>96740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428734</v>
+        <v>428662</v>
       </c>
       <c r="R4" t="n">
-        <v>6232888</v>
+        <v>6232900</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471893</v>
+        <v>121471892</v>
       </c>
       <c r="B5" t="n">
-        <v>96740</v>
+        <v>80264</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428735</v>
+        <v>428712</v>
       </c>
       <c r="R5" t="n">
-        <v>6232886</v>
+        <v>6232901</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471883</v>
+        <v>121471888</v>
       </c>
       <c r="B6" t="n">
-        <v>96740</v>
+        <v>74534</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2606</v>
+        <v>6428</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428493</v>
+        <v>428627</v>
       </c>
       <c r="R6" t="n">
-        <v>6232948</v>
+        <v>6232838</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471890</v>
+        <v>121471883</v>
       </c>
       <c r="B7" t="n">
-        <v>94603</v>
+        <v>96740</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428698</v>
+        <v>428493</v>
       </c>
       <c r="R7" t="n">
-        <v>6232878</v>
+        <v>6232948</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121471889</v>
+        <v>121471890</v>
       </c>
       <c r="B8" t="n">
-        <v>96740</v>
+        <v>94603</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428662</v>
+        <v>428698</v>
       </c>
       <c r="R8" t="n">
-        <v>6232900</v>
+        <v>6232878</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471888</v>
+        <v>121471884</v>
       </c>
       <c r="B9" t="n">
-        <v>74534</v>
+        <v>80251</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6428</v>
+        <v>230185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428627</v>
+        <v>428533</v>
       </c>
       <c r="R9" t="n">
-        <v>6232838</v>
+        <v>6232951</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471892</v>
+        <v>121471894</v>
       </c>
       <c r="B10" t="n">
-        <v>80264</v>
+        <v>94603</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428712</v>
+        <v>428734</v>
       </c>
       <c r="R10" t="n">
-        <v>6232901</v>
+        <v>6232888</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 19019-2024 artfynd.xlsx
+++ b/artfynd/A 19019-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121471893</v>
+        <v>121471885</v>
       </c>
       <c r="B2" t="n">
-        <v>96740</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2606</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428735</v>
+        <v>428621</v>
       </c>
       <c r="R2" t="n">
-        <v>6232886</v>
+        <v>6232812</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121471891</v>
+        <v>121471892</v>
       </c>
       <c r="B3" t="n">
-        <v>96740</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428714</v>
+        <v>428712</v>
       </c>
       <c r="R3" t="n">
-        <v>6232900</v>
+        <v>6232901</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121471889</v>
+        <v>121471883</v>
       </c>
       <c r="B4" t="n">
-        <v>96740</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428662</v>
+        <v>428493</v>
       </c>
       <c r="R4" t="n">
-        <v>6232900</v>
+        <v>6232948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121471892</v>
+        <v>121471889</v>
       </c>
       <c r="B5" t="n">
-        <v>80264</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428712</v>
+        <v>428662</v>
       </c>
       <c r="R5" t="n">
-        <v>6232901</v>
+        <v>6232900</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121471888</v>
+        <v>121471891</v>
       </c>
       <c r="B6" t="n">
-        <v>74534</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428627</v>
+        <v>428714</v>
       </c>
       <c r="R6" t="n">
-        <v>6232838</v>
+        <v>6232900</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121471883</v>
+        <v>121471893</v>
       </c>
       <c r="B7" t="n">
-        <v>96740</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428493</v>
+        <v>428735</v>
       </c>
       <c r="R7" t="n">
-        <v>6232948</v>
+        <v>6232886</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,12 +1260,7 @@
         <v>121471890</v>
       </c>
       <c r="B8" t="n">
-        <v>94603</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121471884</v>
+        <v>121471894</v>
       </c>
       <c r="B9" t="n">
-        <v>80251</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428533</v>
+        <v>428734</v>
       </c>
       <c r="R9" t="n">
-        <v>6232951</v>
+        <v>6232888</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121471894</v>
+        <v>121471887</v>
       </c>
       <c r="B10" t="n">
-        <v>94603</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2671</v>
+        <v>2779</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>428734</v>
+        <v>428640</v>
       </c>
       <c r="R10" t="n">
-        <v>6232888</v>
+        <v>6232808</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,6 +1545,297 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121471888</v>
+      </c>
+      <c r="B11" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>428627</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6232838</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121471886</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>428638</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6232808</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121471884</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ballingslöv, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>428533</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6232951</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19019-2024 artfynd.xlsx
+++ b/artfynd/A 19019-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471885</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471892</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471883</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471889</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471891</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471893</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471890</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471894</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471887</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471888</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471886</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,8 +1896,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121471884</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>